--- a/izakaya-note/dist/rare.xlsx
+++ b/izakaya-note/dist/rare.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27510" windowHeight="16455"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="322">
   <si>
     <t>名称</t>
   </si>
@@ -479,6 +479,21 @@
   </si>
   <si>
     <t>魔法森林、妖怪兽道、人间之里、博丽神社、红魔馆、迷途竹林、妖怪之山、旧地狱、地灵殿、命莲寺、神灵庙、太阳花田、辉针城</t>
+  </si>
+  <si>
+    <t>秦心</t>
+  </si>
+  <si>
+    <t>514-850</t>
+  </si>
+  <si>
+    <t>传说、和风、凉爽、梦幻、适合拍照、招牌、流行·喜爱</t>
+  </si>
+  <si>
+    <t>中酒精、烧酒、甘、古典</t>
+  </si>
+  <si>
+    <t>咸、重油、灼热、流行·厌恶</t>
   </si>
   <si>
     <t>【DLC1】爱丽丝</t>
@@ -992,16 +1007,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1492,137 +1501,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1630,14 +1639,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1986,7 +1992,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.6666666666667" style="1" customWidth="1"/>
@@ -2522,7 +2528,7 @@
       <c r="A27" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -2542,28 +2548,28 @@
       <c r="A28" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>25</v>
+      <c r="B28" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>154</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>90</v>
+      <c r="B29" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>156</v>
@@ -2582,8 +2588,8 @@
       <c r="A30" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>107</v>
+      <c r="B30" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>161</v>
@@ -2602,40 +2608,40 @@
       <c r="A31" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>13</v>
+      <c r="B32" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2643,16 +2649,16 @@
         <v>175</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="D33" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>179</v>
@@ -2663,16 +2669,16 @@
         <v>180</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>42</v>
+        <v>181</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>183</v>
+        <v>48</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>184</v>
@@ -2683,7 +2689,7 @@
         <v>185</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>186</v>
@@ -2703,7 +2709,7 @@
         <v>190</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>191</v>
@@ -2723,47 +2729,47 @@
         <v>195</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="D37" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="D38" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>208</v>
@@ -2783,16 +2789,16 @@
         <v>212</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>216</v>
@@ -2803,16 +2809,16 @@
         <v>217</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="4" t="s">
         <v>218</v>
       </c>
+      <c r="C41" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="D41" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>220</v>
+        <v>48</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>221</v>
@@ -2823,47 +2829,47 @@
         <v>222</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="D42" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>13</v>
+      <c r="B43" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>202</v>
+      <c r="B44" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>233</v>
@@ -2883,19 +2889,19 @@
         <v>237</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="D45" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2912,64 +2918,64 @@
         <v>245</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>158</v>
+        <v>246</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="D47" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="D47" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>251</v>
+      <c r="E47" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>7</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>253</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>202</v>
+        <v>257</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>258</v>
+        <v>136</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>259</v>
@@ -2982,27 +2988,27 @@
       <c r="A50" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="D50" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="E50" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="F50" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="2" t="s">
         <v>267</v>
       </c>
       <c r="C51" s="4" t="s">
@@ -3015,15 +3021,15 @@
         <v>270</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>273</v>
@@ -3042,7 +3048,7 @@
       <c r="A53" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C53" s="4" t="s">
@@ -3055,15 +3061,15 @@
         <v>280</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B54" s="5" t="s">
         <v>282</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>283</v>
@@ -3075,35 +3081,35 @@
         <v>285</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="C55" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="D55" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="E55" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="F55" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>247</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>294</v>
@@ -3111,39 +3117,39 @@
       <c r="D56" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F56" s="4" t="s">
-        <v>292</v>
+      <c r="F56" s="5" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>59</v>
+      <c r="B58" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>303</v>
@@ -3155,15 +3161,15 @@
         <v>305</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B59" s="5" t="s">
         <v>307</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>308</v>
@@ -3172,51 +3178,51 @@
         <v>309</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F59" s="4"/>
+        <v>310</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B60" s="5" t="s">
         <v>311</v>
       </c>
+      <c r="B60" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="C60" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="E60" s="4"/>
+        <v>314</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>163</v>
+      </c>
       <c r="F60" s="4"/>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>48</v>
+        <v>315</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>48</v>
+        <v>317</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B62" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C62" s="4" t="s">
@@ -3234,7 +3240,7 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>48</v>
@@ -3249,6 +3255,26 @@
         <v>48</v>
       </c>
       <c r="F63" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>48</v>
       </c>
     </row>
